--- a/src/windpost-database.xlsx
+++ b/src/windpost-database.xlsx
@@ -2263,7 +2263,7 @@
         <x:v>min_outer_gap_mm</x:v>
       </x:c>
       <x:c r="B15">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" t="str">
         <x:v>Minimum post-to-outer-leaf gap</x:v>

--- a/src/windpost-database.xlsx
+++ b/src/windpost-database.xlsx
@@ -2274,7 +2274,7 @@
         <x:v>min_outer_embedment_mm</x:v>
       </x:c>
       <x:c r="B16">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" t="str">
         <x:v>Minimum outer tie embedment</x:v>
